--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_09_Multi-Agent _ A2A Systems/Day_09_Phan_02_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_09_Multi-Agent _ A2A Systems/Day_09_Phan_02_20_Cau.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I4" s="4" t="n">
@@ -690,7 +690,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Prompt phải nói cả được làm gì và không được làm gì.</t>
+          <t>Một prompt ra quyết định tối thiểu cho supervisor cần: (a) Danh sách các worker kèm bản tóm tắt năng lực cốt lõi; (b) Cấu trúc schema đầu ra được phép trả về; (c) Ranh giới phủ định (negative boundaries: không tự tiện suy đoán trả lời); (d) Hướng dẫn cách xử lý khi đầu vào bị thiếu hoặc mơ hồ. Không đưa toàn bộ chi tiết chính sách nghiệp vụ vào supervisor.</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I6" s="4" t="n">
@@ -799,7 +799,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy hỏi: sai ở bước này có hậu quả gì, và máy có đủ thẩm quyền/bằng chứng không?</t>
+          <t>Các tình huống bắt buộc phải có bước con người kiểm tra/phê duyệt (Human-in-the-Loop): (a) Thao tác hoàn tiền (refund) vượt ngưỡng giá trị quy định; (b) Khi hai nguồn sự thật có thẩm quyền mâu thuẫn trực tiếp và không thể tự phân giải; (c) Yêu cầu cấp quyền có hậu quả lớn nhưng độ tin cậy của mô hình thấp. Các tác vụ đọc thông thường hay tính toán xác định không cần chặn người duyệt.</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4 → o5</t>
+          <t>o2 → o4 → o5 → o1 → o3</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -999,7 +999,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Không thể kiểm tra lời gọi trước khi biết schema được công bố.</t>
+          <t>Trình tự khám phá và gọi công cụ trong giao thức Model Context Protocol (MCP): 1. Client thiết lập kết nối và khởi tạo bắt tay (initialize) với MCP server (o2) -&gt; 2. Client gửi yêu cầu liệt kê danh sách capabilities/tools (tools/list) (o4) -&gt; 3. Đọc name, description, schema và chọn công cụ phù hợp (o5) -&gt; 4. Kiểm tra tính hợp lệ của arguments theo inputSchema đã công bố (o1) -&gt; 5. Thực hiện lời gọi capability/tool (tools/call) (o3).</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
@@ -1156,7 +1156,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Kiểm cả đường khám phá và đường gọi.</t>
+          <t>Bề mặt một công cụ MCP hoàn chỉnh cần bao gồm: (a) Tên và mô tả công cụ ổn định, rõ ràng; (b) Schema dữ liệu đầu vào và đầu ra có định kiểu nghiêm ngặt (JSON Schema); (c) Khả năng đăng ký và điều phối (registry &amp; dispatch); (d) Cơ chế xác thực dữ liệu và trả về lỗi có cấu trúc khi thất bại. Không được phụ thuộc vào chi tiết triển khai nội bộ viết cứng.</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,5</t>
         </is>
       </c>
       <c r="I14" s="4" t="n">
@@ -1208,7 +1208,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hỏi lớp nào vẫn chặn được khi prompt injection khiến model làm theo.</t>
+          <t>Cơ chế bảo mật nhiều lớp (defense-in-depth) cho agent thao tác dữ liệu: (a) Token truy cập cấp quyền tối thiểu (chỉ đọc read-ticket); (b) Các hành động thay đổi dữ liệu có hậu quả (hoàn tiền) phải có phê duyệt và kiểm tra phân quyền độc lập tại máy chủ; (c) MCP server chạy trong môi trường sandbox cô lập an toàn; (e) Kiểm toán và ghi nhật ký toàn bộ tham số tool/hành động. Không bao giờ dựa vào prompt như lớp bảo vệ cuối cùng.</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I15" s="4" t="n">
@@ -1260,7 +1260,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách tính hợp lệ của transport/schema khỏi độ tin cậy về ngữ nghĩa.</t>
+          <t>Trước khi sử dụng kết quả từ MCP tool cho một quyết định cấp quyền có hậu quả, client bắt buộc phải xác minh: (a) Tính xác thực nguồn gốc và thẩm quyền của server (provenance/authority); (b) Phạm vi dữ liệu trả về có đúng người dùng và nhiệm vụ được ủy quyền; (c) Độ tươi mới và phiên bản của dữ liệu (freshness/version); (d) Đánh giá hậu quả và tính tuân thủ chính sách của hành động. Kiểm tra schema transport đơn thuần là chưa đủ.</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
@@ -1517,7 +1517,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Thiết kế cả đường không nhận việc và không hoàn tất.</t>
+          <t>Yêu cầu ủy thác công việc giữa các agent thuộc các bên sở hữu khác nhau (Agent-to-Agent delegation) cần: (a) Định nghĩa nhiệm vụ và ngữ cảnh được giới hạn chặt chẽ; (b) Các ràng buộc và định dạng artifact đầu ra mong đợi; (c) Thời hạn hoàn thành (deadline), trạng thái hoặc cơ chế callback; (d) Ngữ nghĩa rõ ràng cho các trạng thái: nhận việc, từ chối, timeout, và hoàn thành một phần. Tuyệt đối không chia sẻ toàn bộ state nội bộ và bí mật.</t>
         </is>
       </c>
     </row>
